--- a/resources/templates/standard/A7100-02.xlsx
+++ b/resources/templates/standard/A7100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>클린 신고서</t>
   </si>
@@ -611,9 +614,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -632,15 +637,15 @@
     </row>
     <row r="3" ht="20.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -648,21 +653,21 @@
     <row r="4" ht="20.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -907,10 +912,10 @@
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
